--- a/Tagihan/2026/September/Tanjung Putra.xlsx
+++ b/Tagihan/2026/September/Tanjung Putra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\September\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{741C36A2-52D0-41F8-8E5F-0047101A6798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC060BE-7936-405F-9A7D-BEB5F7ADCEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
   <si>
     <t>NO.</t>
   </si>
@@ -185,19 +185,10 @@
     <t>Service AC</t>
   </si>
   <si>
-    <t>AC</t>
-  </si>
-  <si>
     <t>Tambah Freon</t>
   </si>
   <si>
-    <t>CCTV</t>
-  </si>
-  <si>
     <t>Setting dan Konfigurasi CCTV</t>
-  </si>
-  <si>
-    <t>Furniture</t>
   </si>
   <si>
     <t>Perbaikan Laci</t>
@@ -214,8 +205,11 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>14 September 2025</t>
+      <t>22 September 2025</t>
     </r>
+  </si>
+  <si>
+    <t>Kepada Tuan/Nyonya        Tanjung Putra</t>
   </si>
 </sst>
 </file>
@@ -320,7 +314,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -547,63 +541,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -749,17 +691,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1404,7 +1337,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="52" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G13" s="52"/>
     </row>
@@ -1414,7 +1347,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="53" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="G14" s="53"/>
     </row>
@@ -1423,10 +1356,10 @@
       <c r="D15" s="30"/>
     </row>
     <row r="16" spans="2:7" s="1" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -1443,19 +1376,15 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="56"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="34"/>
       <c r="E17" s="34"/>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
     </row>
     <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2">
-        <v>1</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="37" t="s">
         <v>34</v>
       </c>
@@ -1474,11 +1403,9 @@
       </c>
     </row>
     <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
-        <v>2</v>
-      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -1490,29 +1417,25 @@
         <v>250000</v>
       </c>
       <c r="G19" s="25">
-        <f t="shared" si="0"/>
+        <f>F19*D19</f>
         <v>250000</v>
       </c>
     </row>
     <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="58"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="25"/>
       <c r="G20" s="25"/>
     </row>
     <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2">
-        <v>1</v>
-      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
@@ -1521,25 +1444,21 @@
         <v>75000</v>
       </c>
       <c r="G21" s="25">
-        <v>75000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="58"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="23"/>
       <c r="G22" s="25"/>
     </row>
     <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="26" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -1620,7 +1539,7 @@
       <c r="F31" s="49"/>
       <c r="G31" s="27">
         <f>SUM(G17:G30)</f>
-        <v>575000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -1674,7 +1593,7 @@
       <c r="H40" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
@@ -1688,9 +1607,6 @@
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="85" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
